--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="119">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -47,9 +47,6 @@
     <t>TC001</t>
   </si>
   <si>
-    <t>Pending</t>
-  </si>
-  <si>
     <t>TC002</t>
   </si>
   <si>
@@ -119,118 +116,271 @@
     <t>Invoice exists</t>
   </si>
   <si>
-    <t>Payment successful</t>
-  </si>
-  <si>
     <t>API Endpoint</t>
   </si>
   <si>
-    <t>POST /users</t>
-  </si>
-  <si>
-    <t>POST /rooms</t>
-  </si>
-  <si>
     <t>PUT /rooms/{id}</t>
   </si>
   <si>
-    <t>DELETE /rooms/{id}</t>
-  </si>
-  <si>
-    <t>POST /tenants</t>
-  </si>
-  <si>
-    <t>PUT /tenants/{id}</t>
-  </si>
-  <si>
-    <t>POST /contracts</t>
-  </si>
-  <si>
-    <t>GET /contracts/{id}</t>
-  </si>
-  <si>
-    <t>POST /invoices</t>
-  </si>
-  <si>
-    <t>POST /payments</t>
-  </si>
-  <si>
     <t>User Management</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>Send POST /users with valid data</t>
-  </si>
-  <si>
     <t>User created successfully</t>
   </si>
   <si>
-    <t>Send POST /users with invalid data</t>
-  </si>
-  <si>
     <t>Error message returned</t>
   </si>
   <si>
     <t>User exists</t>
   </si>
   <si>
-    <t>Send GET /users</t>
-  </si>
-  <si>
     <t>Return list of users</t>
   </si>
   <si>
-    <t>GET /users</t>
-  </si>
-  <si>
-    <t>Send POST /rooms with valid data</t>
-  </si>
-  <si>
-    <t>Send PUT /rooms/{id}</t>
-  </si>
-  <si>
     <t>Room updated successfully</t>
   </si>
   <si>
-    <t>Send DELETE /rooms/{id}</t>
-  </si>
-  <si>
     <t>Room deleted successfully</t>
   </si>
   <si>
-    <t>Send POST /tenants with valid room id</t>
-  </si>
-  <si>
-    <t>Tenant added successfully</t>
-  </si>
-  <si>
-    <t>Send PUT /tenants/{id}</t>
-  </si>
-  <si>
     <t>Tenant updated successfully</t>
   </si>
   <si>
     <t>Tenant &amp; Room exist</t>
   </si>
   <si>
-    <t>Send POST /contracts</t>
-  </si>
-  <si>
-    <t>Send GET /contracts/{id}</t>
-  </si>
-  <si>
     <t>Contract details returned</t>
   </si>
   <si>
-    <t>Send POST /invoices</t>
-  </si>
-  <si>
-    <t>Send POST /payments</t>
-  </si>
-  <si>
     <t>Pass</t>
+  </si>
+  <si>
+    <t>POST /api/users</t>
+  </si>
+  <si>
+    <t>GET /api/users</t>
+  </si>
+  <si>
+    <t>POST /api/rooms</t>
+  </si>
+  <si>
+    <t>POST /api/tenants</t>
+  </si>
+  <si>
+    <t>POST /api/contracts</t>
+  </si>
+  <si>
+    <t>Test Type</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Send POST /api/users with valid data</t>
+  </si>
+  <si>
+    <t>Send POST /api/users with invalid data</t>
+  </si>
+  <si>
+    <t>Error 400</t>
+  </si>
+  <si>
+    <t>BUG01</t>
+  </si>
+  <si>
+    <t>Send GET /api/users</t>
+  </si>
+  <si>
+    <t>Send POST/api /rooms with valid data</t>
+  </si>
+  <si>
+    <t>Room created successfully</t>
+  </si>
+  <si>
+    <t>Send PUT /api/rooms/{id}</t>
+  </si>
+  <si>
+    <t>Send DELETE/api /rooms/{id}</t>
+  </si>
+  <si>
+    <t>DELETE /api/rooms/{id}</t>
+  </si>
+  <si>
+    <t>Send POST/api /tenants with valid room id</t>
+  </si>
+  <si>
+    <t>Error 500</t>
+  </si>
+  <si>
+    <t>BUG02</t>
+  </si>
+  <si>
+    <t>Send PUT /api/tenants/{id}</t>
+  </si>
+  <si>
+    <t>PUT /api/tenants/{id}</t>
+  </si>
+  <si>
+    <t>Contract created successfully</t>
+  </si>
+  <si>
+    <t>Send POST /api/contracts</t>
+  </si>
+  <si>
+    <t>Send GET/api /contracts/{id}</t>
+  </si>
+  <si>
+    <t>GET /api/contracts/{id}</t>
+  </si>
+  <si>
+    <t>POST/api /invoices</t>
+  </si>
+  <si>
+    <t>POST/api /payments</t>
+  </si>
+  <si>
+    <t>Send POST /api/invoices with negative amount</t>
+  </si>
+  <si>
+    <t>Invoice created with negative amount</t>
+  </si>
+  <si>
+    <t>BUG03</t>
+  </si>
+  <si>
+    <t>Send POST /api/payments with invalid invoice id</t>
+  </si>
+  <si>
+    <t>BUG04</t>
+  </si>
+  <si>
+    <t>TC013</t>
+  </si>
+  <si>
+    <t>TC014</t>
+  </si>
+  <si>
+    <t>TC015</t>
+  </si>
+  <si>
+    <t>TC016</t>
+  </si>
+  <si>
+    <t>TC017</t>
+  </si>
+  <si>
+    <t>TC018</t>
+  </si>
+  <si>
+    <t>TC019</t>
+  </si>
+  <si>
+    <t>TC020</t>
+  </si>
+  <si>
+    <t>Login UI</t>
+  </si>
+  <si>
+    <t>Open login page → enter valid username &amp; password → click login</t>
+  </si>
+  <si>
+    <t>User login successfully and redirect to dashboard</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Enter wrong password → click login</t>
+  </si>
+  <si>
+    <t>Show error message</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Room UI</t>
+  </si>
+  <si>
+    <t>Logged in</t>
+  </si>
+  <si>
+    <t>Go to Room page → click Add → enter data → save</t>
+  </si>
+  <si>
+    <t>Room appears in list</t>
+  </si>
+  <si>
+    <t>Click Edit room → update info → save</t>
+  </si>
+  <si>
+    <t>Room updated</t>
+  </si>
+  <si>
+    <t>Tenant UI</t>
+  </si>
+  <si>
+    <t>Contract UI</t>
+  </si>
+  <si>
+    <t>Invoice UI</t>
+  </si>
+  <si>
+    <t>Payment UI</t>
+  </si>
+  <si>
+    <t>Go to Tenant page → add tenant → select room → save</t>
+  </si>
+  <si>
+    <t>Tenant added</t>
+  </si>
+  <si>
+    <t>Create contract via UI</t>
+  </si>
+  <si>
+    <t>Create invoice via UI</t>
+  </si>
+  <si>
+    <t>Record payment</t>
+  </si>
+  <si>
+    <t>Payment success</t>
+  </si>
+  <si>
+    <t>Login successful, redirected to dashboard, user session created</t>
+  </si>
+  <si>
+    <t>Error message displayed: "Invalid username or password", login not allowed</t>
+  </si>
+  <si>
+    <t>Room added successfully, new room displayed in room list with correct information</t>
+  </si>
+  <si>
+    <t>Room updated successfully, updated information displayed correctly in UI</t>
+  </si>
+  <si>
+    <t>Tenant added successfully, tenant appears in list and linked to selected room</t>
+  </si>
+  <si>
+    <t>Contract created successfully, contract information displayed correctly</t>
+  </si>
+  <si>
+    <t>Invoice created successfully, invoice displayed with correct amount and status</t>
+  </si>
+  <si>
+    <t>Payment recorded successfully, invoice status updated accordingly</t>
   </si>
 </sst>
 </file>
@@ -294,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -302,9 +452,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -586,20 +752,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.33203125" customWidth="1"/>
-    <col min="4" max="4" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.109375" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="9" customWidth="1"/>
+    <col min="8" max="8" width="28.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="105.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,326 +784,628 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="42" x14ac:dyDescent="0.3">
+      <c r="H1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="H2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="G5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" ht="42" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="G9" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="H9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" ht="42" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="G10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="H10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="I12" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="D17" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="D19" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="F19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="D20" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="F20" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10" ht="21" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="D21" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J21" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/test-cases.xlsx
+++ b/docs/test-cases.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="121">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -194,9 +194,6 @@
     <t>Send POST /api/users with invalid data</t>
   </si>
   <si>
-    <t>Error 400</t>
-  </si>
-  <si>
     <t>BUG01</t>
   </si>
   <si>
@@ -381,6 +378,15 @@
   </si>
   <si>
     <t>Payment recorded successfully, invoice status updated accordingly</t>
+  </si>
+  <si>
+    <t>User created successfully with empty fields, no validation applied</t>
+  </si>
+  <si>
+    <t>Tenant created successfully, new tenant returned with id = X and correct data</t>
+  </si>
+  <si>
+    <t>Tenant created successfully</t>
   </si>
 </sst>
 </file>
@@ -444,7 +450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -462,7 +468,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -758,11 +763,11 @@
     <col min="1" max="1" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.33203125" customWidth="1"/>
-    <col min="4" max="4" width="66.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="9" customWidth="1"/>
-    <col min="8" max="8" width="28.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="85" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="8" customWidth="1"/>
+    <col min="8" max="8" width="28.21875" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="105.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
@@ -815,10 +820,10 @@
       <c r="E2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -845,20 +850,20 @@
       <c r="E3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>50</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="21" x14ac:dyDescent="0.4">
@@ -872,15 +877,15 @@
         <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -902,22 +907,22 @@
         <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -932,15 +937,15 @@
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -962,15 +967,15 @@
         <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="F7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -992,25 +997,25 @@
         <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>50</v>
+      <c r="G8" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I8" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="21" x14ac:dyDescent="0.4">
@@ -1024,15 +1029,15 @@
         <v>18</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H9" s="3" t="s">
@@ -1054,22 +1059,22 @@
         <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J10" s="6"/>
     </row>
@@ -1084,15 +1089,15 @@
         <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>43</v>
       </c>
       <c r="H11" s="3" t="s">
@@ -1114,25 +1119,25 @@
         <v>23</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="10" t="s">
+      <c r="F12" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>50</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I12" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="21" x14ac:dyDescent="0.4">
@@ -1146,264 +1151,264 @@
         <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>50</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>53</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="F14" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>91</v>
-      </c>
       <c r="I14" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>91</v>
+      <c r="H15" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J15" s="6"/>
     </row>
     <row r="16" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>91</v>
+      <c r="F16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J16" s="6"/>
     </row>
     <row r="17" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>91</v>
+      <c r="F17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>91</v>
+      <c r="F18" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J18" s="6"/>
     </row>
     <row r="19" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="7" t="s">
+      <c r="D19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>91</v>
+      <c r="F19" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J19" s="6"/>
     </row>
     <row r="20" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" s="7" t="s">
+      <c r="D20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>91</v>
+      <c r="F20" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" ht="21" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>91</v>
+      <c r="F21" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J21" s="6"/>
     </row>
